--- a/AAII_Financials/Yearly/PSHG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PSHG_YR_FIN.xlsx
@@ -1275,13 +1275,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>7500</v>
+        <v>5600</v>
       </c>
       <c r="E22" s="3">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="F22" s="3">
-        <v>21000</v>
+        <v>8500</v>
       </c>
       <c r="G22" s="3">
         <v>27800</v>
@@ -1320,13 +1320,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>48100</v>
+        <v>50000</v>
       </c>
       <c r="E23" s="3">
-        <v>41900</v>
+        <v>43700</v>
       </c>
       <c r="F23" s="3">
-        <v>56900</v>
+        <v>69400</v>
       </c>
       <c r="G23" s="3">
         <v>12000</v>
@@ -1455,13 +1455,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>48100</v>
+        <v>50000</v>
       </c>
       <c r="E26" s="3">
-        <v>41900</v>
+        <v>43700</v>
       </c>
       <c r="F26" s="3">
-        <v>56900</v>
+        <v>69400</v>
       </c>
       <c r="G26" s="3">
         <v>12000</v>
@@ -1500,13 +1500,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>48100</v>
+        <v>50000</v>
       </c>
       <c r="E27" s="3">
-        <v>41900</v>
+        <v>43700</v>
       </c>
       <c r="F27" s="3">
-        <v>56900</v>
+        <v>69400</v>
       </c>
       <c r="G27" s="3">
         <v>12000</v>
@@ -1770,13 +1770,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>48100</v>
+        <v>50000</v>
       </c>
       <c r="E33" s="3">
-        <v>41900</v>
+        <v>43700</v>
       </c>
       <c r="F33" s="3">
-        <v>56900</v>
+        <v>69400</v>
       </c>
       <c r="G33" s="3">
         <v>12000</v>
@@ -1860,13 +1860,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>48100</v>
+        <v>50000</v>
       </c>
       <c r="E35" s="3">
-        <v>41900</v>
+        <v>43700</v>
       </c>
       <c r="F35" s="3">
-        <v>56900</v>
+        <v>69400</v>
       </c>
       <c r="G35" s="3">
         <v>12000</v>
@@ -3630,13 +3630,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>48100</v>
+        <v>50000</v>
       </c>
       <c r="E81" s="3">
-        <v>41900</v>
+        <v>43700</v>
       </c>
       <c r="F81" s="3">
-        <v>56900</v>
+        <v>69400</v>
       </c>
       <c r="G81" s="3">
         <v>12000</v>
